--- a/cypress/downloads/resultsApproval_NewBuildMacro.xlsx
+++ b/cypress/downloads/resultsApproval_NewBuildMacro.xlsx
@@ -421,7 +421,7 @@
         <v>Pass</v>
       </c>
       <c r="C2" t="str">
-        <v>2025-08-29T03:52:35.411Z</v>
+        <v>2025-08-31T05:07:37.253Z</v>
       </c>
     </row>
     <row r="3">
@@ -432,7 +432,7 @@
         <v>Pass</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-08-29T03:52:51.739Z</v>
+        <v>2025-08-31T05:07:53.043Z</v>
       </c>
     </row>
     <row r="4">
@@ -443,7 +443,7 @@
         <v>Pass</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-08-29T03:52:53.308Z</v>
+        <v>2025-08-31T05:07:54.487Z</v>
       </c>
     </row>
   </sheetData>

--- a/cypress/downloads/resultsApproval_NewBuildMacro.xlsx
+++ b/cypress/downloads/resultsApproval_NewBuildMacro.xlsx
@@ -397,10 +397,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:E8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="C1" t="str">
+        <v>timeStamp</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Timestamp</v>
+      </c>
+      <c r="E1" t="str">
+        <v>TimeStamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>User AM melakukan akses ke menu Stip Approval</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-03-05T01:25:18.575Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>User AM melakukan klik tombol Search di Stip approval</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-05T01:25:25.127Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>User AM melakukan klik tombol Search di Stip approval</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-05T01:25:25.468Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>User LEAD PM melakukan akses ke menu Stip Approval</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-03-05T01:26:23.844Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>User LEAD PM melakukan input SONumber di Stip approval</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2026-03-05T01:26:31.814Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>User AM melakukan klik tombol Search di Stip approval</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-05T01:26:32.452Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>User AM melakukan klik tombol Search di Stip approval</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-05T01:26:32.706Z</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/downloads/resultsApproval_NewBuildMacro.xlsx
+++ b/cypress/downloads/resultsApproval_NewBuildMacro.xlsx
@@ -397,105 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Test</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="C1" t="str">
-        <v>timeStamp</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Timestamp</v>
-      </c>
-      <c r="E1" t="str">
-        <v>TimeStamp</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>User AM melakukan akses ke menu Stip Approval</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Pass</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2026-03-05T01:25:18.575Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>User AM melakukan klik tombol Search di Stip approval</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Pass</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-05T01:25:25.127Z</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>User AM melakukan klik tombol Search di Stip approval</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Pass</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-05T01:25:25.468Z</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>User LEAD PM melakukan akses ke menu Stip Approval</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Pass</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-03-05T01:26:23.844Z</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>User LEAD PM melakukan input SONumber di Stip approval</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Pass</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2026-03-05T01:26:31.814Z</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>User AM melakukan klik tombol Search di Stip approval</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Pass</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-05T01:26:32.452Z</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>User AM melakukan klik tombol Search di Stip approval</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Pass</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-05T01:26:32.706Z</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/downloads/resultsApproval_NewBuildMacro.xlsx
+++ b/cypress/downloads/resultsApproval_NewBuildMacro.xlsx
@@ -397,10 +397,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:D4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="C1" t="str">
+        <v>timeStamp</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Timestamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>User PM FO melakukan akses ke menu Project activity Header</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-04-02T08:59:07.471Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>User AM melakukan klik tombol Search di Stip approval</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-02T08:59:24.193Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>User AM melakukan klik tombol Search di Stip approval</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-02T08:59:25.639Z</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>